--- a/Resources/experiments/result.xlsx
+++ b/Resources/experiments/result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sabi\gogogo\KIT\Abschlussarbeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83CE5498-1777-4640-A22B-C2D925A1053B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5980B68-DBB5-4D35-AB86-14474287CBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{B6222BE5-703D-4CA7-8A0E-616DC73853A6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="10" xr2:uid="{B6222BE5-703D-4CA7-8A0E-616DC73853A6}"/>
   </bookViews>
   <sheets>
     <sheet name="intro_20260526" sheetId="7" r:id="rId1"/>
@@ -18,15 +18,24 @@
     <sheet name="sum_orient_20260526" sheetId="6" r:id="rId3"/>
     <sheet name="sum_pos_20260526" sheetId="8" r:id="rId4"/>
     <sheet name="sum_fail_20260526" sheetId="9" r:id="rId5"/>
-    <sheet name="intro_20260605" sheetId="14" r:id="rId6"/>
+    <sheet name="intro_20260605" sheetId="16" r:id="rId6"/>
     <sheet name="result_20260605" sheetId="10" r:id="rId7"/>
     <sheet name="sum_orient_20260605" sheetId="11" r:id="rId8"/>
     <sheet name="sum_pos_20260605" sheetId="12" r:id="rId9"/>
     <sheet name="sum_fail_20260605" sheetId="13" r:id="rId10"/>
+    <sheet name="intro_20260611" sheetId="14" r:id="rId11"/>
+    <sheet name="result_20260611" sheetId="15" r:id="rId12"/>
+    <sheet name="sum_orient_20260611" sheetId="17" r:id="rId13"/>
+    <sheet name="sum_pos_20260611" sheetId="18" r:id="rId14"/>
+    <sheet name="sum_fail_20260611" sheetId="19" r:id="rId15"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId16"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">result_20260526!$A$1:$P$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">result_20260605!$A$1:$Q$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">result_20260611!$A$1:$Q$164</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="78">
   <si>
     <t>Success</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -276,10 +285,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>grasp_cog_dist_th</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>grasp_cog_min_dist_th</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -340,6 +345,30 @@
   </si>
   <si>
     <t>xyz=(0,0,0.25)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>grasp_cog_max_dist_th</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grasp too close to the object</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grasp point not good, potential failure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object not face out after placement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grasp aborted due to joint limits</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grasp point too low, placement distant from holder</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1418,7 +1447,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>sum_fail_20260605!$B$1</c:f>
+              <c:f>[1]sum_fail_20260605!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1439,7 +1468,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>sum_fail_20260605!$A$2:$A$10</c:f>
+              <c:f>[1]sum_fail_20260605!$A$2:$A$10</c:f>
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
@@ -1474,7 +1503,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>sum_fail_20260605!$B$2:$B$10</c:f>
+              <c:f>[1]sum_fail_20260605!$B$2:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1510,7 +1539,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5E16-4BDE-84B9-47AC61CEA0FF}"/>
+              <c16:uniqueId val="{00000000-D1B0-4A86-AC01-285725CB0892}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1536,7 +1565,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>sum_fail_20260605!$C$1</c15:sqref>
+                          <c15:sqref>[1]sum_fail_20260605!$C$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1563,7 +1592,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>sum_fail_20260605!$A$2:$A$10</c15:sqref>
+                          <c15:sqref>[1]sum_fail_20260605!$A$2:$A$10</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1604,12 +1633,12 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>sum_fail_20260605!$C$2:$C$10</c15:sqref>
+                          <c15:sqref>[1]sum_fail_20260605!$C$2:$C$10</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:numCache>
-                      <c:formatCode>0.00%</c:formatCode>
+                      <c:formatCode>General</c:formatCode>
                       <c:ptCount val="9"/>
                       <c:pt idx="0">
                         <c:v>0</c:v>
@@ -1643,7 +1672,7 @@
                 </c:val>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000001-5E16-4BDE-84B9-47AC61CEA0FF}"/>
+                    <c16:uniqueId val="{00000001-D1B0-4A86-AC01-285725CB0892}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -2306,6 +2335,950 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sum_fail_20260611!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>sum_fail_20260611!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Grasp point not good, potential failure</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>No poses generated</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Grasp too close to the object</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Grasp too loose</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Grasp point too low, placement distant from holder</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Grasp in opposite direction</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Possible collision between links</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Grasp aborted due to joint limits</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Object not face out after placement</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sum_fail_20260611!$B$2:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8A4D-4237-A316-83DF039547FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1160082432"/>
+        <c:axId val="1160089152"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>sum_fail_20260611!$C$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Percentage</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>sum_fail_20260611!$A$2:$A$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="9"/>
+                      <c:pt idx="0">
+                        <c:v>Grasp point not good, potential failure</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>No poses generated</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Grasp too close to the object</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Grasp too loose</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>Grasp point too low, placement distant from holder</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>Grasp in opposite direction</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>Possible collision between links</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>Grasp aborted due to joint limits</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>Object not face out after placement</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>sum_fail_20260611!$C$2:$C$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="9"/>
+                      <c:pt idx="0">
+                        <c:v>9.375E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.21875</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.46875</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3.125E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1.09375</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>0.34375</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>0.40625</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>0.59375</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-8A4D-4237-A316-83DF039547FA}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1160082432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1160089152"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1160089152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1160082432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1200"/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>sum_fail_20260611!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>sum_fail_20260611!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Grasp point not good, potential failure</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>No poses generated</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Grasp too close to the object</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Grasp too loose</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Grasp point too low, placement distant from holder</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Grasp in opposite direction</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Possible collision between links</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Grasp aborted due to joint limits</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Object not face out after placement</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>sum_fail_20260611!$B$2:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97D8-4E02-B526-31B02880F698}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1160082432"/>
+        <c:axId val="1160089152"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>sum_fail_20260611!$C$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Percentage</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>sum_fail_20260611!$A$2:$A$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="9"/>
+                      <c:pt idx="0">
+                        <c:v>Grasp point not good, potential failure</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>No poses generated</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Grasp too close to the object</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Grasp too loose</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>Grasp point too low, placement distant from holder</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>Grasp in opposite direction</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>Possible collision between links</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>Grasp aborted due to joint limits</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>Object not face out after placement</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>sum_fail_20260611!$C$2:$C$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.00%</c:formatCode>
+                      <c:ptCount val="9"/>
+                      <c:pt idx="0">
+                        <c:v>9.375E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.21875</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.46875</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3.125E-2</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1.09375</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>0.34375</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>0.40625</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>0.59375</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-97D8-4E02-B526-31B02880F698}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1160082432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1160089152"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1160089152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1160082432"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2387,6 +3360,86 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3941,6 +4994,1016 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -4001,10 +6064,10 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B5ADE9F-9A38-45A7-9C1C-CDB92977BA59}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9A574BD-9B94-4B83-A2D3-D3B727793949}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4066,6 +6129,329 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1171575</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>852488</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC329A3D-0625-4712-96E4-50C94EB4EB00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>109536</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7C3BC05-D447-4AFE-B89E-3C89F96A7A87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="General"/>
+      <sheetName val="Position"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="intro_20260526"/>
+      <sheetName val="result_20260526"/>
+      <sheetName val="sum_orient_20260526"/>
+      <sheetName val="sum_pos_20260526"/>
+      <sheetName val="sum_fail_20260526"/>
+      <sheetName val="intro_20260605"/>
+      <sheetName val="result_20260605"/>
+      <sheetName val="sum_orient_20260605"/>
+      <sheetName val="sum_pos_20260605"/>
+      <sheetName val="sum_fail_20260605"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
+        <row r="2">
+          <cell r="P2">
+            <v>0.59259259259259256</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="P3">
+            <v>7.407407407407407E-2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="P4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="P5">
+            <v>0.88888888888888884</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="P6">
+            <v>0.3888888888888889</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="P7">
+            <v>0.3888888888888889</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="P8">
+            <v>0.22222222222222221</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="P9">
+            <v>0.72222222222222221</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="12">
+        <row r="2">
+          <cell r="P2">
+            <v>0.45833333333333331</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="P3">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="P4">
+            <v>0.33333333333333331</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="P5">
+            <v>0.375</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="P6">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="P7">
+            <v>0.5</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="P8">
+            <v>0.33333333333333331</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="P9">
+            <v>0.16666666666666666</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="P10">
+            <v>0.41666666666666669</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="13">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>Count</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>Percentage</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>Grasp point not good</v>
+          </cell>
+          <cell r="B2">
+            <v>0</v>
+          </cell>
+          <cell r="C2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>No poses generated</v>
+          </cell>
+          <cell r="B3">
+            <v>1</v>
+          </cell>
+          <cell r="C3">
+            <v>1.0309278350515464E-2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>No poses generated because of noise</v>
+          </cell>
+          <cell r="B4">
+            <v>0</v>
+          </cell>
+          <cell r="C4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Grasp too loose</v>
+          </cell>
+          <cell r="B5">
+            <v>70</v>
+          </cell>
+          <cell r="C5">
+            <v>0.72164948453608246</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>Gripper stuck in foam</v>
+          </cell>
+          <cell r="B6">
+            <v>2</v>
+          </cell>
+          <cell r="C6">
+            <v>2.0618556701030927E-2</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>Grasp in opposite direction</v>
+          </cell>
+          <cell r="B7">
+            <v>0</v>
+          </cell>
+          <cell r="C7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>Possible collision between links</v>
+          </cell>
+          <cell r="B8">
+            <v>14</v>
+          </cell>
+          <cell r="C8">
+            <v>0.14432989690721648</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>Object fell during turning around</v>
+          </cell>
+          <cell r="B9">
+            <v>10</v>
+          </cell>
+          <cell r="C9">
+            <v>0.10309278350515463</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>Placement not good</v>
+          </cell>
+          <cell r="B10">
+            <v>6</v>
+          </cell>
+          <cell r="C10">
+            <v>6.1855670103092786E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4595,16 +6981,16 @@
         <v>55</v>
       </c>
       <c r="I12" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="J12" s="48" t="s">
+      <c r="K12" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="48" t="s">
+      <c r="L12" s="48" t="s">
         <v>58</v>
-      </c>
-      <c r="L12" s="48" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="30" customHeight="1">
@@ -4636,30 +7022,30 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="30" customHeight="1">
       <c r="C14" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="E14" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="52" t="s">
+      <c r="F14" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="G14" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="52" t="s">
+      <c r="H14" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="I14" s="52" t="s">
         <v>66</v>
-      </c>
-      <c r="I14" s="52" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="30" customHeight="1">
@@ -4798,7 +7184,7 @@
         <v>0.29166666666666669</v>
       </c>
     </row>
-    <row r="22" spans="3:14" ht="30" customHeight="1">
+    <row r="22" spans="3:14" ht="15" customHeight="1">
       <c r="C22" s="17" t="s">
         <v>7</v>
       </c>
@@ -4809,7 +7195,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="3:14" ht="30" customHeight="1">
+    <row r="23" spans="3:14" ht="15" customHeight="1">
       <c r="C23" s="15">
         <f>sum_pos_20260526!O3</f>
         <v>0.5</v>
@@ -4956,7 +7342,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5">
         <f>result_20260605!L164</f>
@@ -4969,7 +7355,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <f>result_20260605!M164</f>
@@ -5109,6 +7495,5529 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{9A27859D-0026-4028-9EDE-0556E0D9CCDA}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFF555A"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C2:C10</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D18726E8-315C-407A-8A20-ADEECEB211C9}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="B3:O32"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="30" customHeight="1"/>
+  <sheetData>
+    <row r="3" spans="2:15" ht="30" customHeight="1" thickBot="1">
+      <c r="B3" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+    </row>
+    <row r="4" spans="2:15" ht="30" customHeight="1">
+      <c r="B4" s="26"/>
+      <c r="C4" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="26"/>
+      <c r="G4" s="30">
+        <v>1</v>
+      </c>
+      <c r="H4" s="31">
+        <v>2</v>
+      </c>
+      <c r="I4" s="31">
+        <v>3</v>
+      </c>
+      <c r="J4" s="31">
+        <v>4</v>
+      </c>
+      <c r="K4" s="31">
+        <v>5</v>
+      </c>
+      <c r="L4" s="31">
+        <v>6</v>
+      </c>
+      <c r="M4" s="31">
+        <v>7</v>
+      </c>
+      <c r="N4" s="32">
+        <v>8</v>
+      </c>
+      <c r="O4" s="26"/>
+    </row>
+    <row r="5" spans="2:15" ht="30" customHeight="1">
+      <c r="B5" s="26"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="26"/>
+    </row>
+    <row r="6" spans="2:15" ht="30" customHeight="1" thickBot="1">
+      <c r="B6" s="26"/>
+      <c r="C6" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="26"/>
+      <c r="G6" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="2:15" ht="30" customHeight="1">
+      <c r="B7" s="26"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+    </row>
+    <row r="8" spans="2:15" ht="30" customHeight="1">
+      <c r="B8" s="26"/>
+      <c r="C8" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+    </row>
+    <row r="9" spans="2:15" ht="30" customHeight="1" thickBot="1">
+      <c r="B9" s="26"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+    </row>
+    <row r="10" spans="2:15" ht="30" customHeight="1">
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+    </row>
+    <row r="11" spans="2:15" s="47" customFormat="1" ht="14.25"/>
+    <row r="12" spans="2:15" ht="60" customHeight="1">
+      <c r="B12" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="48" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" ht="30" customHeight="1">
+      <c r="C13" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="49">
+        <v>0.2</v>
+      </c>
+      <c r="H13" s="49">
+        <v>2E-3</v>
+      </c>
+      <c r="I13" s="49">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J13" s="49">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="L13" s="51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" ht="30" customHeight="1">
+      <c r="C14" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="52" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" ht="30" customHeight="1">
+      <c r="C15" s="51">
+        <v>1.447416</v>
+      </c>
+      <c r="D15" s="51">
+        <v>3.302368</v>
+      </c>
+      <c r="E15" s="51">
+        <v>1.3658980000000001</v>
+      </c>
+      <c r="F15" s="51">
+        <v>-9.5960000000000004E-3</v>
+      </c>
+      <c r="G15" s="51">
+        <v>0.99959399999999998</v>
+      </c>
+      <c r="H15" s="51">
+        <v>2.5939E-2</v>
+      </c>
+      <c r="I15" s="51">
+        <v>-6.796E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" ht="30" customHeight="1" thickBot="1"/>
+    <row r="18" spans="3:14" ht="30" customHeight="1" thickBot="1">
+      <c r="D18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1</v>
+      </c>
+      <c r="H18" s="6">
+        <v>2</v>
+      </c>
+      <c r="I18" s="6">
+        <v>3</v>
+      </c>
+      <c r="J18" s="6">
+        <v>4</v>
+      </c>
+      <c r="K18" s="6">
+        <v>5</v>
+      </c>
+      <c r="L18" s="6">
+        <v>6</v>
+      </c>
+      <c r="M18" s="6">
+        <v>7</v>
+      </c>
+      <c r="N18" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" ht="30" customHeight="1" thickBot="1">
+      <c r="G19" s="22">
+        <f>sum_orient_20260611!P2</f>
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="H19" s="9">
+        <f>sum_orient_20260611!P3</f>
+        <v>1</v>
+      </c>
+      <c r="I19" s="9">
+        <f>sum_orient_20260611!P4</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="9">
+        <f>sum_orient_20260611!P5</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="K19" s="9">
+        <f>sum_orient_20260611!P6</f>
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="L19" s="9">
+        <f>sum_orient_20260611!P7</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="9">
+        <f>sum_orient_20260611!P8</f>
+        <v>0.5</v>
+      </c>
+      <c r="N19" s="23">
+        <f>sum_orient_20260611!P9</f>
+        <v>0.94444444444444442</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" ht="30" customHeight="1" thickBot="1">
+      <c r="C20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" ht="30" customHeight="1">
+      <c r="C21" s="15">
+        <f>sum_pos_20260611!P2</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D21" s="11">
+        <f>sum_pos_20260611!P5</f>
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="E21" s="16">
+        <f>sum_pos_20260611!P8</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" ht="15" customHeight="1">
+      <c r="C22" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" ht="15" customHeight="1">
+      <c r="C23" s="15">
+        <f>sum_pos_20260611!P3</f>
+        <v>1</v>
+      </c>
+      <c r="D23" s="11">
+        <f>sum_pos_20260611!P6</f>
+        <v>1</v>
+      </c>
+      <c r="E23" s="16">
+        <f>sum_pos_20260611!P9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" ht="30" customHeight="1">
+      <c r="C24" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" ht="30" customHeight="1" thickBot="1">
+      <c r="C25" s="19">
+        <f>sum_pos_20260611!P4</f>
+        <v>0.875</v>
+      </c>
+      <c r="D25" s="20">
+        <f>sum_pos_20260611!P7</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E25" s="21">
+        <f>sum_pos_20260611!P10</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" s="47" customFormat="1" ht="10.5" customHeight="1"/>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C4:E9">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:E25">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19:N19">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F154A264-8280-4B21-9C82-9393E7D2D089}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:Q164"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="9" max="9" width="13.625" customWidth="1"/>
+    <col min="10" max="10" width="17.25" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="13" width="31" customWidth="1"/>
+    <col min="14" max="14" width="14.625" customWidth="1"/>
+    <col min="15" max="15" width="19.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="str">
+        <f t="shared" ref="D2:D65" si="0">A2&amp;"-"&amp;B2&amp;"-"&amp;C2</f>
+        <v>1-A-1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" si="0"/>
+        <v>1-A-2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>1-A-3</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>1-B-1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>1-B-2</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>1-B-3</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>1-C-1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>1-C-2</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>1-C-3</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>1-D-1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>1-D-2</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>1-D-3</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>1-E-1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>1-E-2</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>1-E-3</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>1-F-1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>1-F-2</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>1-F-3</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>1-G-1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>1-G-2</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v>1-G-3</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="0"/>
+        <v>1-H-1</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v>1-H-2</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v>1-H-3</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v>1-I-1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="0"/>
+        <v>1-I-2</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="0"/>
+        <v>1-I-3</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v>2-A-1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="0"/>
+        <v>2-A-2</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="0"/>
+        <v>2-A-3</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" si="0"/>
+        <v>2-B-1</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="str">
+        <f t="shared" si="0"/>
+        <v>2-B-2</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" si="0"/>
+        <v>2-B-3</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35">
+        <v>2</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" t="str">
+        <f t="shared" si="0"/>
+        <v>2-C-1</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36">
+        <v>2</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="0"/>
+        <v>2-C-2</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37">
+        <v>2</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="0"/>
+        <v>2-C-3</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="M37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38">
+        <v>2</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="0"/>
+        <v>2-D-1</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="M38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39">
+        <v>2</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" si="0"/>
+        <v>2-D-2</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="0"/>
+        <v>2-D-3</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="M40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="0"/>
+        <v>2-E-1</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="M41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="0"/>
+        <v>2-E-2</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="0"/>
+        <v>2-E-3</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="0"/>
+        <v>2-F-1</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45">
+        <v>2</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="0"/>
+        <v>2-F-2</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="0"/>
+        <v>2-F-3</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="M46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47">
+        <v>2</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="0"/>
+        <v>2-G-1</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="0"/>
+        <v>2-G-2</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="M48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>2</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" si="0"/>
+        <v>2-G-3</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="M49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>2</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" si="0"/>
+        <v>2-H-1</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="M50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="0"/>
+        <v>2-H-2</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="0"/>
+        <v>2-H-3</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="0"/>
+        <v>2-I-1</v>
+      </c>
+      <c r="F53">
+        <v>1</v>
+      </c>
+      <c r="M53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="0"/>
+        <v>2-I-2</v>
+      </c>
+      <c r="F54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>2</v>
+      </c>
+      <c r="B55" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="0"/>
+        <v>2-I-3</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="0"/>
+        <v>3-A-1</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="0"/>
+        <v>3-A-2</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="O57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="0"/>
+        <v>3-A-3</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="O58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>3</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="0"/>
+        <v>3-C-1</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="0"/>
+        <v>3-C-2</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="0"/>
+        <v>3-C-3</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="0"/>
+        <v>3-D-1</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="P62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
+      <c r="A63">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="0"/>
+        <v>3-D-2</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="O63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="str">
+        <f t="shared" si="0"/>
+        <v>3-D-3</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="O64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="0"/>
+        <v>3-F-1</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="O65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" ref="D66:D129" si="1">A66&amp;"-"&amp;B66&amp;"-"&amp;C66</f>
+        <v>3-F-2</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="O66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" si="1"/>
+        <v>3-F-3</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="1"/>
+        <v>3-G-1</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69">
+        <v>3</v>
+      </c>
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="1"/>
+        <v>3-G-2</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="O69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70">
+        <v>3</v>
+      </c>
+      <c r="B70" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="str">
+        <f t="shared" si="1"/>
+        <v>3-G-3</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="O70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
+      <c r="A71">
+        <v>3</v>
+      </c>
+      <c r="B71" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="1"/>
+        <v>3-I-1</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
+      <c r="A72">
+        <v>3</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="1"/>
+        <v>3-I-2</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="P72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="A73">
+        <v>3</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="str">
+        <f t="shared" si="1"/>
+        <v>3-I-3</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="P73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="A74">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74" t="str">
+        <f t="shared" si="1"/>
+        <v>4-A-1</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="P74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75">
+        <v>4</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75" t="str">
+        <f t="shared" si="1"/>
+        <v>4-A-2</v>
+      </c>
+      <c r="E75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76" t="str">
+        <f t="shared" si="1"/>
+        <v>4-A-3</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77">
+        <v>4</v>
+      </c>
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="str">
+        <f t="shared" si="1"/>
+        <v>4-C-1</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="A78">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78" t="str">
+        <f t="shared" si="1"/>
+        <v>4-C-2</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="A79">
+        <v>4</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79" t="str">
+        <f t="shared" si="1"/>
+        <v>4-C-3</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80" t="str">
+        <f t="shared" si="1"/>
+        <v>4-D-1</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17">
+      <c r="A81">
+        <v>4</v>
+      </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81" t="str">
+        <f t="shared" si="1"/>
+        <v>4-D-2</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17">
+      <c r="A82">
+        <v>4</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82" t="str">
+        <f t="shared" si="1"/>
+        <v>4-D-3</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="Q82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17">
+      <c r="A83">
+        <v>4</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" t="str">
+        <f t="shared" si="1"/>
+        <v>4-F-1</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17">
+      <c r="A84">
+        <v>4</v>
+      </c>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84" t="str">
+        <f t="shared" si="1"/>
+        <v>4-F-2</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17">
+      <c r="A85">
+        <v>4</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85" t="str">
+        <f t="shared" si="1"/>
+        <v>4-F-3</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17">
+      <c r="A86">
+        <v>4</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86" t="str">
+        <f t="shared" si="1"/>
+        <v>4-G-1</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17">
+      <c r="A87">
+        <v>4</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87" t="str">
+        <f t="shared" si="1"/>
+        <v>4-G-2</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17">
+      <c r="A88">
+        <v>4</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88" t="str">
+        <f t="shared" si="1"/>
+        <v>4-G-3</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17">
+      <c r="A89">
+        <v>4</v>
+      </c>
+      <c r="B89" t="s">
+        <v>14</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89" t="str">
+        <f t="shared" si="1"/>
+        <v>4-I-1</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17">
+      <c r="A90">
+        <v>4</v>
+      </c>
+      <c r="B90" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90" t="str">
+        <f t="shared" si="1"/>
+        <v>4-I-2</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17">
+      <c r="A91">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91" t="str">
+        <f t="shared" si="1"/>
+        <v>4-I-3</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17">
+      <c r="A92">
+        <v>5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92" t="str">
+        <f t="shared" si="1"/>
+        <v>5-A-1</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17">
+      <c r="A93">
+        <v>5</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" t="str">
+        <f t="shared" si="1"/>
+        <v>5-A-2</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17">
+      <c r="A94">
+        <v>5</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94" t="str">
+        <f t="shared" si="1"/>
+        <v>5-A-3</v>
+      </c>
+      <c r="E94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17">
+      <c r="A95">
+        <v>5</v>
+      </c>
+      <c r="B95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95" t="str">
+        <f t="shared" si="1"/>
+        <v>5-C-1</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17">
+      <c r="A96">
+        <v>5</v>
+      </c>
+      <c r="B96" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96" t="str">
+        <f t="shared" si="1"/>
+        <v>5-C-2</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="Q96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17">
+      <c r="A97">
+        <v>5</v>
+      </c>
+      <c r="B97" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97">
+        <v>3</v>
+      </c>
+      <c r="D97" t="str">
+        <f t="shared" si="1"/>
+        <v>5-C-3</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="Q97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17">
+      <c r="A98">
+        <v>5</v>
+      </c>
+      <c r="B98" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98" t="str">
+        <f t="shared" si="1"/>
+        <v>5-D-1</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17">
+      <c r="A99">
+        <v>5</v>
+      </c>
+      <c r="B99" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" t="str">
+        <f t="shared" si="1"/>
+        <v>5-D-2</v>
+      </c>
+      <c r="E99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17">
+      <c r="A100">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100" t="str">
+        <f t="shared" si="1"/>
+        <v>5-D-3</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17">
+      <c r="A101">
+        <v>5</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101" t="str">
+        <f t="shared" si="1"/>
+        <v>5-F-1</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17">
+      <c r="A102">
+        <v>5</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102" t="str">
+        <f t="shared" si="1"/>
+        <v>5-F-2</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17">
+      <c r="A103">
+        <v>5</v>
+      </c>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103">
+        <v>3</v>
+      </c>
+      <c r="D103" t="str">
+        <f t="shared" si="1"/>
+        <v>5-F-3</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17">
+      <c r="A104">
+        <v>5</v>
+      </c>
+      <c r="B104" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="str">
+        <f t="shared" si="1"/>
+        <v>5-G-1</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="Q104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17">
+      <c r="A105">
+        <v>5</v>
+      </c>
+      <c r="B105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105" t="str">
+        <f t="shared" si="1"/>
+        <v>5-G-2</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17">
+      <c r="A106">
+        <v>5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106" t="str">
+        <f t="shared" si="1"/>
+        <v>5-G-3</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17">
+      <c r="A107">
+        <v>5</v>
+      </c>
+      <c r="B107" t="s">
+        <v>14</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107" t="str">
+        <f t="shared" si="1"/>
+        <v>5-I-1</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17">
+      <c r="A108">
+        <v>5</v>
+      </c>
+      <c r="B108" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108" t="str">
+        <f t="shared" si="1"/>
+        <v>5-I-2</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="Q108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17">
+      <c r="A109">
+        <v>5</v>
+      </c>
+      <c r="B109" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109">
+        <v>3</v>
+      </c>
+      <c r="D109" t="str">
+        <f t="shared" si="1"/>
+        <v>5-I-3</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17">
+      <c r="A110">
+        <v>6</v>
+      </c>
+      <c r="B110" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110" t="str">
+        <f t="shared" si="1"/>
+        <v>6-A-1</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17">
+      <c r="A111">
+        <v>6</v>
+      </c>
+      <c r="B111" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111" t="str">
+        <f t="shared" si="1"/>
+        <v>6-A-2</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17">
+      <c r="A112">
+        <v>6</v>
+      </c>
+      <c r="B112" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112">
+        <v>3</v>
+      </c>
+      <c r="D112" t="str">
+        <f t="shared" si="1"/>
+        <v>6-A-3</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13">
+      <c r="A113">
+        <v>6</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113" t="str">
+        <f t="shared" si="1"/>
+        <v>6-C-1</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13">
+      <c r="A114">
+        <v>6</v>
+      </c>
+      <c r="B114" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114">
+        <v>2</v>
+      </c>
+      <c r="D114" t="str">
+        <f t="shared" si="1"/>
+        <v>6-C-2</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13">
+      <c r="A115">
+        <v>6</v>
+      </c>
+      <c r="B115" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
+      <c r="D115" t="str">
+        <f t="shared" si="1"/>
+        <v>6-C-3</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116">
+        <v>6</v>
+      </c>
+      <c r="B116" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116" t="str">
+        <f t="shared" si="1"/>
+        <v>6-D-1</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13">
+      <c r="A117">
+        <v>6</v>
+      </c>
+      <c r="B117" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117">
+        <v>2</v>
+      </c>
+      <c r="D117" t="str">
+        <f t="shared" si="1"/>
+        <v>6-D-2</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13">
+      <c r="A118">
+        <v>6</v>
+      </c>
+      <c r="B118" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118">
+        <v>3</v>
+      </c>
+      <c r="D118" t="str">
+        <f t="shared" si="1"/>
+        <v>6-D-3</v>
+      </c>
+      <c r="E118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119">
+        <v>6</v>
+      </c>
+      <c r="B119" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119" t="str">
+        <f t="shared" si="1"/>
+        <v>6-F-1</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120">
+        <v>6</v>
+      </c>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="D120" t="str">
+        <f t="shared" si="1"/>
+        <v>6-F-2</v>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121">
+        <v>6</v>
+      </c>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121">
+        <v>3</v>
+      </c>
+      <c r="D121" t="str">
+        <f t="shared" si="1"/>
+        <v>6-F-3</v>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="A122">
+        <v>6</v>
+      </c>
+      <c r="B122" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122" t="str">
+        <f t="shared" si="1"/>
+        <v>6-G-1</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13">
+      <c r="A123">
+        <v>6</v>
+      </c>
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123" t="str">
+        <f t="shared" si="1"/>
+        <v>6-G-2</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13">
+      <c r="A124">
+        <v>6</v>
+      </c>
+      <c r="B124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="D124" t="str">
+        <f t="shared" si="1"/>
+        <v>6-G-3</v>
+      </c>
+      <c r="E124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13">
+      <c r="A125">
+        <v>6</v>
+      </c>
+      <c r="B125" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125" t="str">
+        <f t="shared" si="1"/>
+        <v>6-I-1</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13">
+      <c r="A126">
+        <v>6</v>
+      </c>
+      <c r="B126" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126">
+        <v>2</v>
+      </c>
+      <c r="D126" t="str">
+        <f t="shared" si="1"/>
+        <v>6-I-2</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13">
+      <c r="A127">
+        <v>6</v>
+      </c>
+      <c r="B127" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127">
+        <v>3</v>
+      </c>
+      <c r="D127" t="str">
+        <f t="shared" si="1"/>
+        <v>6-I-3</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13">
+      <c r="A128">
+        <v>7</v>
+      </c>
+      <c r="B128" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128" t="str">
+        <f t="shared" si="1"/>
+        <v>7-A-1</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
+      <c r="A129">
+        <v>7</v>
+      </c>
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129" t="str">
+        <f t="shared" si="1"/>
+        <v>7-A-2</v>
+      </c>
+      <c r="E129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
+      <c r="A130">
+        <v>7</v>
+      </c>
+      <c r="B130" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130">
+        <v>3</v>
+      </c>
+      <c r="D130" t="str">
+        <f t="shared" ref="D130:D163" si="2">A130&amp;"-"&amp;B130&amp;"-"&amp;C130</f>
+        <v>7-A-3</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="P130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
+      <c r="A131">
+        <v>7</v>
+      </c>
+      <c r="B131" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131" t="str">
+        <f t="shared" si="2"/>
+        <v>7-C-1</v>
+      </c>
+      <c r="E131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
+      <c r="A132">
+        <v>7</v>
+      </c>
+      <c r="B132" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132" t="str">
+        <f t="shared" si="2"/>
+        <v>7-C-2</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133">
+        <v>7</v>
+      </c>
+      <c r="B133" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133">
+        <v>3</v>
+      </c>
+      <c r="D133" t="str">
+        <f t="shared" si="2"/>
+        <v>7-C-3</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134">
+        <v>7</v>
+      </c>
+      <c r="B134" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134" t="str">
+        <f t="shared" si="2"/>
+        <v>7-D-1</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135">
+        <v>7</v>
+      </c>
+      <c r="B135" t="s">
+        <v>9</v>
+      </c>
+      <c r="C135">
+        <v>2</v>
+      </c>
+      <c r="D135" t="str">
+        <f t="shared" si="2"/>
+        <v>7-D-2</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="P135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136">
+        <v>7</v>
+      </c>
+      <c r="B136" t="s">
+        <v>9</v>
+      </c>
+      <c r="C136">
+        <v>3</v>
+      </c>
+      <c r="D136" t="str">
+        <f t="shared" si="2"/>
+        <v>7-D-3</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="P136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
+      <c r="A137">
+        <v>7</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137" t="str">
+        <f t="shared" si="2"/>
+        <v>7-F-1</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="M137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
+      <c r="A138">
+        <v>7</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138">
+        <v>2</v>
+      </c>
+      <c r="D138" t="str">
+        <f t="shared" si="2"/>
+        <v>7-F-2</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="M138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
+      <c r="A139">
+        <v>7</v>
+      </c>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139">
+        <v>3</v>
+      </c>
+      <c r="D139" t="str">
+        <f t="shared" si="2"/>
+        <v>7-F-3</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="P139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
+      <c r="A140">
+        <v>7</v>
+      </c>
+      <c r="B140" t="s">
+        <v>12</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140" t="str">
+        <f t="shared" si="2"/>
+        <v>7-G-1</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="P140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141">
+        <v>7</v>
+      </c>
+      <c r="B141" t="s">
+        <v>12</v>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+      <c r="D141" t="str">
+        <f t="shared" si="2"/>
+        <v>7-G-2</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="P141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142">
+        <v>7</v>
+      </c>
+      <c r="B142" t="s">
+        <v>12</v>
+      </c>
+      <c r="C142">
+        <v>3</v>
+      </c>
+      <c r="D142" t="str">
+        <f t="shared" si="2"/>
+        <v>7-G-3</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="P142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143">
+        <v>7</v>
+      </c>
+      <c r="B143" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143" t="str">
+        <f t="shared" si="2"/>
+        <v>7-I-1</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144">
+        <v>7</v>
+      </c>
+      <c r="B144" t="s">
+        <v>14</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144" t="str">
+        <f t="shared" si="2"/>
+        <v>7-I-2</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+      <c r="P144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17">
+      <c r="A145">
+        <v>7</v>
+      </c>
+      <c r="B145" t="s">
+        <v>14</v>
+      </c>
+      <c r="C145">
+        <v>3</v>
+      </c>
+      <c r="D145" t="str">
+        <f t="shared" si="2"/>
+        <v>7-I-3</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="P145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17">
+      <c r="A146">
+        <v>8</v>
+      </c>
+      <c r="B146" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146" t="str">
+        <f t="shared" si="2"/>
+        <v>8-A-1</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="Q146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17">
+      <c r="A147">
+        <v>8</v>
+      </c>
+      <c r="B147" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147">
+        <v>2</v>
+      </c>
+      <c r="D147" t="str">
+        <f t="shared" si="2"/>
+        <v>8-A-2</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="Q147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17">
+      <c r="A148">
+        <v>8</v>
+      </c>
+      <c r="B148" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148">
+        <v>3</v>
+      </c>
+      <c r="D148" t="str">
+        <f t="shared" si="2"/>
+        <v>8-A-3</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="Q148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17">
+      <c r="A149">
+        <v>8</v>
+      </c>
+      <c r="B149" t="s">
+        <v>8</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149" t="str">
+        <f t="shared" si="2"/>
+        <v>8-C-1</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17">
+      <c r="A150">
+        <v>8</v>
+      </c>
+      <c r="B150" t="s">
+        <v>8</v>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+      <c r="D150" t="str">
+        <f t="shared" si="2"/>
+        <v>8-C-2</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17">
+      <c r="A151">
+        <v>8</v>
+      </c>
+      <c r="B151" t="s">
+        <v>8</v>
+      </c>
+      <c r="C151">
+        <v>3</v>
+      </c>
+      <c r="D151" t="str">
+        <f t="shared" si="2"/>
+        <v>8-C-3</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17">
+      <c r="A152">
+        <v>8</v>
+      </c>
+      <c r="B152" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="str">
+        <f t="shared" si="2"/>
+        <v>8-D-1</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="K152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17">
+      <c r="A153">
+        <v>8</v>
+      </c>
+      <c r="B153" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153">
+        <v>2</v>
+      </c>
+      <c r="D153" t="str">
+        <f t="shared" si="2"/>
+        <v>8-D-2</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17">
+      <c r="A154">
+        <v>8</v>
+      </c>
+      <c r="B154" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154">
+        <v>3</v>
+      </c>
+      <c r="D154" t="str">
+        <f t="shared" si="2"/>
+        <v>8-D-3</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17">
+      <c r="A155">
+        <v>8</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155" t="str">
+        <f t="shared" si="2"/>
+        <v>8-F-1</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17">
+      <c r="A156">
+        <v>8</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156">
+        <v>2</v>
+      </c>
+      <c r="D156" t="str">
+        <f t="shared" si="2"/>
+        <v>8-F-2</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17">
+      <c r="A157">
+        <v>8</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157">
+        <v>3</v>
+      </c>
+      <c r="D157" t="str">
+        <f t="shared" si="2"/>
+        <v>8-F-3</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17">
+      <c r="A158">
+        <v>8</v>
+      </c>
+      <c r="B158" t="s">
+        <v>12</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158" t="str">
+        <f t="shared" si="2"/>
+        <v>8-G-1</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17">
+      <c r="A159">
+        <v>8</v>
+      </c>
+      <c r="B159" t="s">
+        <v>12</v>
+      </c>
+      <c r="C159">
+        <v>2</v>
+      </c>
+      <c r="D159" t="str">
+        <f t="shared" si="2"/>
+        <v>8-G-2</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17">
+      <c r="A160">
+        <v>8</v>
+      </c>
+      <c r="B160" t="s">
+        <v>12</v>
+      </c>
+      <c r="C160">
+        <v>3</v>
+      </c>
+      <c r="D160" t="str">
+        <f t="shared" si="2"/>
+        <v>8-G-3</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17">
+      <c r="A161">
+        <v>8</v>
+      </c>
+      <c r="B161" t="s">
+        <v>14</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161" t="str">
+        <f t="shared" si="2"/>
+        <v>8-I-1</v>
+      </c>
+      <c r="H161">
+        <v>1</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17">
+      <c r="A162">
+        <v>8</v>
+      </c>
+      <c r="B162" t="s">
+        <v>14</v>
+      </c>
+      <c r="C162">
+        <v>2</v>
+      </c>
+      <c r="D162" t="str">
+        <f t="shared" si="2"/>
+        <v>8-I-2</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="Q162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17">
+      <c r="A163">
+        <v>8</v>
+      </c>
+      <c r="B163" t="s">
+        <v>14</v>
+      </c>
+      <c r="C163">
+        <v>3</v>
+      </c>
+      <c r="D163" t="str">
+        <f t="shared" si="2"/>
+        <v>8-I-3</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="Q163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17">
+      <c r="A164" t="s">
+        <v>39</v>
+      </c>
+      <c r="B164" t="s">
+        <v>39</v>
+      </c>
+      <c r="C164" t="s">
+        <v>39</v>
+      </c>
+      <c r="D164" t="s">
+        <v>39</v>
+      </c>
+      <c r="E164">
+        <f>SUM(E2:E163)</f>
+        <v>59</v>
+      </c>
+      <c r="F164">
+        <f t="shared" ref="F164:Q164" si="3">SUM(F2:F163)</f>
+        <v>69</v>
+      </c>
+      <c r="G164">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="I164">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J164">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="K164">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="L164">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M164">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="N164">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="P164">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="Q164">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q164" xr:uid="{BB563E77-EE44-42B3-ACD0-800B48D3E7DF}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{233F4877-837B-41BB-A651-CAFC9A749971}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="3" max="3" width="12.75" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.625" customWidth="1"/>
+    <col min="9" max="10" width="18.25" customWidth="1"/>
+    <col min="14" max="14" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>9</v>
+      </c>
+      <c r="O2">
+        <f>SUM(B2:E2)</f>
+        <v>27</v>
+      </c>
+      <c r="P2" s="8">
+        <f>SUM(B2+C2)/O2</f>
+        <v>0.96296296296296291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>27</v>
+      </c>
+      <c r="D3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>27</v>
+      </c>
+      <c r="K3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O9" si="0">SUM(B3:E3)</f>
+        <v>27</v>
+      </c>
+      <c r="P3" s="8">
+        <f t="shared" ref="P3:P10" si="1">SUM(B3+C3)/O3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>11</v>
+      </c>
+      <c r="M4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="N4">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P4" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" si="1"/>
+        <v>0.88888888888888884</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P6" s="8">
+        <f t="shared" si="1"/>
+        <v>0.94444444444444442</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="P7" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>9</v>
+      </c>
+      <c r="N8">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P8" s="8">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P9" s="8">
+        <f t="shared" si="1"/>
+        <v>0.94444444444444442</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="24">
+        <f>SUM(B2:B9)</f>
+        <v>59</v>
+      </c>
+      <c r="C10" s="24">
+        <f t="shared" ref="C10:O10" si="2">SUM(C2:C9)</f>
+        <v>69</v>
+      </c>
+      <c r="D10" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="24">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="F10" s="24">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="G10" s="24">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="I10" s="24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J10" s="24">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="K10" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="24">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="M10" s="24">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="N10" s="24">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="O10" s="24">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+      <c r="P10" s="25">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="P2">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="percent" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P10">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB486FB-0CFA-4051-92D9-62519C2C1B14}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5" style="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A2,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>6</v>
+      </c>
+      <c r="O2">
+        <f t="shared" ref="O2:O10" si="0">SUM(B2:E2)</f>
+        <v>24</v>
+      </c>
+      <c r="P2" s="8">
+        <f t="shared" ref="P2:P10" si="1">SUM(B2:C2)/O2</f>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A3,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="P3" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A4,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="P4" s="8">
+        <f t="shared" si="1"/>
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" si="1"/>
+        <v>0.77272727272727271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A6,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="P6" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="P7" s="8">
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="K8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A8,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="P8" s="8">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A9,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="P9" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!B$1,result_20260611!$1:$1,0)))</f>
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!E$1,result_20260611!$1:$1,0)))</f>
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!F$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!G$1,result_20260611!$1:$1,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!H$1,result_20260611!$1:$1,0)))</f>
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!I$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!J$1,result_20260611!$1:$1,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="K10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!K$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!L$1,result_20260611!$1:$1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!M$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="N10">
+        <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A10,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!N$1,result_20260611!$1:$1,0)))</f>
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="P10" s="8">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="24">
+        <f>SUM(B2:B10)</f>
+        <v>59</v>
+      </c>
+      <c r="C11" s="24">
+        <f t="shared" ref="C11:O11" si="2">SUM(C2:C10)</f>
+        <v>69</v>
+      </c>
+      <c r="D11" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="24">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="F11" s="24">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="G11" s="24">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="I11" s="24">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J11" s="24">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="K11" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="24">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="M11" s="24">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="N11" s="24">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="O11" s="24">
+        <f t="shared" si="2"/>
+        <v>160</v>
+      </c>
+      <c r="P11" s="25">
+        <f t="shared" ref="P11" si="3">SUM(B11+C11)/O11</f>
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="P2:P11">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D435AA-845C-483A-B5EE-3DD22E6E4A30}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="35.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="8" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2">
+        <f>result_20260611!I164</f>
+        <v>3</v>
+      </c>
+      <c r="C2" s="8">
+        <f>B2/$B$19</f>
+        <v>9.375E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>result_20260611!J164</f>
+        <v>7</v>
+      </c>
+      <c r="C3" s="8">
+        <f t="shared" ref="C3:C10" si="0">B3/$B$19</f>
+        <v>0.21875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4">
+        <f>result_20260611!K164</f>
+        <v>15</v>
+      </c>
+      <c r="C4" s="8">
+        <f t="shared" si="0"/>
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5">
+        <f>result_20260611!L164</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="8">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6">
+        <f>result_20260611!M164</f>
+        <v>35</v>
+      </c>
+      <c r="C6" s="8">
+        <f t="shared" si="0"/>
+        <v>1.09375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <f>result_20260611!N164</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <f>result_20260611!O164</f>
+        <v>11</v>
+      </c>
+      <c r="C8" s="8">
+        <f t="shared" si="0"/>
+        <v>0.34375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9">
+        <f>result_20260611!P164</f>
+        <v>13</v>
+      </c>
+      <c r="C9" s="8">
+        <f t="shared" si="0"/>
+        <v>0.40625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10">
+        <f>result_20260611!Q164</f>
+        <v>19</v>
+      </c>
+      <c r="C10" s="8">
+        <f t="shared" si="0"/>
+        <v>0.59375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <f>result_20260611!E164</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <f>result_20260611!F164</f>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16">
+        <f>result_20260611!G164</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <f>result_20260611!H164</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" s="8" customFormat="1">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18">
+        <f>SUM(result_20260611!E164:H164)</f>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" s="8" customFormat="1">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19">
+        <f>SUM(result_20260611!G164:H164)</f>
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C2:C10">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F00E0267-8AA7-4A82-9F06-8A12998832EB}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F00E0267-8AA7-4A82-9F06-8A12998832EB}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -10093,7 +18002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D18726E8-315C-407A-8A20-ADEECEB211C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B6AD1C-F23B-457C-BC16-0C31B8A7B64D}">
   <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
@@ -10283,7 +18192,7 @@
     <row r="11" spans="2:15" s="47" customFormat="1" ht="14.25"/>
     <row r="12" spans="2:15" ht="60" customHeight="1">
       <c r="B12" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="48" t="s">
         <v>53</v>
@@ -10304,16 +18213,16 @@
         <v>55</v>
       </c>
       <c r="I12" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="J12" s="48" t="s">
+      <c r="K12" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="48" t="s">
+      <c r="L12" s="48" t="s">
         <v>58</v>
-      </c>
-      <c r="L12" s="48" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="30" customHeight="1">
@@ -10324,7 +18233,7 @@
         <v>48</v>
       </c>
       <c r="E13" s="49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F13" s="49" t="s">
         <v>52</v>
@@ -10345,30 +18254,30 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="30" customHeight="1">
       <c r="C14" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="E14" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="52" t="s">
+      <c r="F14" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="G14" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="52" t="s">
+      <c r="H14" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="I14" s="52" t="s">
         <v>66</v>
-      </c>
-      <c r="I14" s="52" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="30" customHeight="1">
@@ -10426,35 +18335,35 @@
     </row>
     <row r="19" spans="3:14" ht="30" customHeight="1" thickBot="1">
       <c r="G19" s="22">
-        <f>sum_orient_20260605!P2</f>
+        <f>[1]sum_orient_20260605!P2</f>
         <v>0.59259259259259256</v>
       </c>
       <c r="H19" s="9">
-        <f>sum_orient_20260605!P3</f>
+        <f>[1]sum_orient_20260605!P3</f>
         <v>7.407407407407407E-2</v>
       </c>
       <c r="I19" s="9">
-        <f>sum_orient_20260605!P4</f>
+        <f>[1]sum_orient_20260605!P4</f>
         <v>0</v>
       </c>
       <c r="J19" s="9">
-        <f>sum_orient_20260605!P5</f>
+        <f>[1]sum_orient_20260605!P5</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="K19" s="9">
-        <f>sum_orient_20260605!P6</f>
+        <f>[1]sum_orient_20260605!P6</f>
         <v>0.3888888888888889</v>
       </c>
       <c r="L19" s="9">
-        <f>sum_orient_20260605!P7</f>
+        <f>[1]sum_orient_20260605!P7</f>
         <v>0.3888888888888889</v>
       </c>
       <c r="M19" s="9">
-        <f>sum_orient_20260605!P8</f>
+        <f>[1]sum_orient_20260605!P8</f>
         <v>0.22222222222222221</v>
       </c>
       <c r="N19" s="23">
-        <f>sum_orient_20260605!P9</f>
+        <f>[1]sum_orient_20260605!P9</f>
         <v>0.72222222222222221</v>
       </c>
     </row>
@@ -10495,19 +18404,19 @@
     </row>
     <row r="21" spans="3:14" ht="30" customHeight="1">
       <c r="C21" s="15">
-        <f>sum_pos_20260605!P2</f>
+        <f>[1]sum_pos_20260605!P2</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="D21" s="11">
-        <f>sum_pos_20260605!P5</f>
+        <f>[1]sum_pos_20260605!P5</f>
         <v>0.375</v>
       </c>
       <c r="E21" s="16">
-        <f>sum_pos_20260605!P8</f>
+        <f>[1]sum_pos_20260605!P8</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="22" spans="3:14" ht="30" customHeight="1">
+    <row r="22" spans="3:14" ht="15" customHeight="1">
       <c r="C22" s="17" t="s">
         <v>7</v>
       </c>
@@ -10518,17 +18427,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="3:14" ht="30" customHeight="1">
+    <row r="23" spans="3:14" ht="15" customHeight="1">
       <c r="C23" s="15">
-        <f>sum_pos_20260605!P3</f>
+        <f>[1]sum_pos_20260605!P3</f>
         <v>0.5</v>
       </c>
       <c r="D23" s="11">
-        <f>sum_pos_20260605!P6</f>
+        <f>[1]sum_pos_20260605!P6</f>
         <v>0.5</v>
       </c>
       <c r="E23" s="16">
-        <f>sum_pos_20260605!P9</f>
+        <f>[1]sum_pos_20260605!P9</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -10545,15 +18454,15 @@
     </row>
     <row r="25" spans="3:14" ht="30" customHeight="1" thickBot="1">
       <c r="C25" s="19">
-        <f>sum_pos_20260605!P4</f>
+        <f>[1]sum_pos_20260605!P4</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="D25" s="20">
-        <f>sum_pos_20260605!P7</f>
+        <f>[1]sum_pos_20260605!P7</f>
         <v>0.5</v>
       </c>
       <c r="E25" s="21">
-        <f>sum_pos_20260605!P10</f>
+        <f>[1]sum_pos_20260605!P10</f>
         <v>0.41666666666666669</v>
       </c>
     </row>
@@ -10561,6 +18470,18 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C4:E9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:E25">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -10572,20 +18493,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:E25">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="G19:N19">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10652,7 +18561,7 @@
         <v>22</v>
       </c>
       <c r="L1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M1" t="s">
         <v>2</v>
@@ -14013,7 +21922,7 @@
         <v>22</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J1" s="24" t="s">
         <v>2</v>
@@ -14691,7 +22600,7 @@
         <v>22</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J1" s="24" t="s">
         <v>2</v>

--- a/Resources/experiments/result.xlsx
+++ b/Resources/experiments/result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sabi\gogogo\KIT\Abschlussarbeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5980B68-DBB5-4D35-AB86-14474287CBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C8BB59-1705-46BE-9CB3-C2AD586DCF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="10" xr2:uid="{B6222BE5-703D-4CA7-8A0E-616DC73853A6}"/>
   </bookViews>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="D21" s="11">
         <f>sum_pos_20260611!P5</f>
-        <v>0.77272727272727271</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="E21" s="16">
         <f>sum_pos_20260611!P8</f>
@@ -10366,6 +10366,9 @@
         <f t="shared" si="1"/>
         <v>6-D-1</v>
       </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
       <c r="M116">
         <v>1</v>
       </c>
@@ -10384,6 +10387,9 @@
         <f t="shared" si="1"/>
         <v>6-D-2</v>
       </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
       <c r="M117">
         <v>1</v>
       </c>
@@ -11331,7 +11337,7 @@
       </c>
       <c r="F164">
         <f t="shared" ref="F164:Q164" si="3">SUM(F2:F163)</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G164">
         <f t="shared" si="3"/>
@@ -11789,7 +11795,7 @@
       </c>
       <c r="C7">
         <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!C$1,result_20260611!$1:$1,0)))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <f>SUMIF(result_20260611!$A:$A,sum_orient_20260611!$A7,INDEX(result_20260611!$A:$Z,0,MATCH(sum_orient_20260611!D$1,result_20260611!$1:$1,0)))</f>
@@ -11837,7 +11843,7 @@
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P7" s="8">
         <f t="shared" si="1"/>
@@ -11984,7 +11990,7 @@
       </c>
       <c r="C10" s="24">
         <f t="shared" ref="C10:O10" si="2">SUM(C2:C9)</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D10" s="24">
         <f t="shared" si="2"/>
@@ -12032,11 +12038,11 @@
       </c>
       <c r="O10" s="24">
         <f t="shared" si="2"/>
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P10" s="25">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>0.80246913580246915</v>
       </c>
     </row>
   </sheetData>
@@ -12337,7 +12343,7 @@
       </c>
       <c r="C5">
         <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!C$1,result_20260611!$1:$1,0)))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <f>SUMIF(result_20260611!$B:$B,sum_pos_20260611!$A5,INDEX(result_20260611!$A:$Z,0,MATCH(sum_pos_20260611!D$1,result_20260611!$1:$1,0)))</f>
@@ -12385,11 +12391,11 @@
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="1"/>
-        <v>0.77272727272727271</v>
+        <v>0.79166666666666663</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -12727,7 +12733,7 @@
       </c>
       <c r="C11" s="24">
         <f t="shared" ref="C11:O11" si="2">SUM(C2:C10)</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D11" s="24">
         <f t="shared" si="2"/>
@@ -12775,11 +12781,11 @@
       </c>
       <c r="O11" s="24">
         <f t="shared" si="2"/>
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P11" s="25">
         <f t="shared" ref="P11" si="3">SUM(B11+C11)/O11</f>
-        <v>0.8</v>
+        <v>0.80246913580246915</v>
       </c>
     </row>
   </sheetData>
@@ -12956,7 +12962,7 @@
       </c>
       <c r="B15">
         <f>result_20260611!F164</f>
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -12983,7 +12989,7 @@
       </c>
       <c r="B18">
         <f>SUM(result_20260611!E164:H164)</f>
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="8" customFormat="1">

--- a/Resources/experiments/result.xlsx
+++ b/Resources/experiments/result.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sabi\gogogo\KIT\Abschlussarbeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC7D08F-9B7F-4522-9262-A8A22E5FB103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4668AA7-3105-4339-93E6-4C99DE7EFD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6222BE5-703D-4CA7-8A0E-616DC73853A6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="8" activeTab="11" xr2:uid="{B6222BE5-703D-4CA7-8A0E-616DC73853A6}"/>
   </bookViews>
   <sheets>
     <sheet name="intro_20260622" sheetId="24" r:id="rId1"/>
@@ -28,10 +28,8 @@
     <sheet name="sum_orient_20260611" sheetId="17" r:id="rId13"/>
     <sheet name="sum_pos_20260611" sheetId="18" r:id="rId14"/>
     <sheet name="sum_fail_20260611" sheetId="19" r:id="rId15"/>
+    <sheet name="Sheet1" sheetId="25" r:id="rId16"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId16"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">result_20260605!$A$1:$Q$164</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">result_20260611!$A$1:$Q$164</definedName>
@@ -80,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="111">
   <si>
     <t>Success</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -501,6 +499,26 @@
   </si>
   <si>
     <t>Final</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Baseline1 vs Baseline2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Failure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Estimated</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chi2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3342,135 +3360,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="General"/>
-      <sheetName val="Position"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="intro_20260526"/>
-      <sheetName val="result_20260526"/>
-      <sheetName val="sum_orient_20260526"/>
-      <sheetName val="sum_pos_20260526"/>
-      <sheetName val="sum_fail_20260526"/>
-      <sheetName val="intro_20260605"/>
-      <sheetName val="result_20260605"/>
-      <sheetName val="sum_orient_20260605"/>
-      <sheetName val="sum_pos_20260605"/>
-      <sheetName val="sum_fail_20260605"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11">
-        <row r="2">
-          <cell r="P2">
-            <v>0.59259259259259256</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="P3">
-            <v>7.407407407407407E-2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="P4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="P5">
-            <v>0.88888888888888884</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="P6">
-            <v>0.3888888888888889</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="P7">
-            <v>0.3888888888888889</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="P8">
-            <v>0.22222222222222221</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="P9">
-            <v>0.72222222222222221</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="12">
-        <row r="2">
-          <cell r="P2">
-            <v>0.45833333333333331</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="P3">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="P4">
-            <v>0.33333333333333331</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="P5">
-            <v>0.375</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="P6">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="P7">
-            <v>0.5</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="P8">
-            <v>0.33333333333333331</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="P9">
-            <v>0.16666666666666666</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="P10">
-            <v>0.41666666666666669</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="13"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3792,7 +3681,7 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="B3:O32"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="15.59765625" defaultRowHeight="30" customHeight="1"/>
   <sheetData>
     <row r="3" spans="2:15" ht="30" customHeight="1" thickBot="1">
       <c r="B3" s="26" t="s">
@@ -3974,7 +3863,7 @@
       <c r="N10" s="26"/>
       <c r="O10" s="26"/>
     </row>
-    <row r="11" spans="2:15" s="47" customFormat="1" ht="14.25"/>
+    <row r="11" spans="2:15" s="47" customFormat="1" ht="13.9"/>
     <row r="12" spans="2:15" ht="60" customHeight="1">
       <c r="B12" s="50" t="s">
         <v>101</v>
@@ -4303,12 +4192,12 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="30.5" customWidth="1"/>
-    <col min="2" max="2" width="8.25" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.625" customWidth="1"/>
+    <col min="1" max="1" width="30.46484375" customWidth="1"/>
+    <col min="2" max="2" width="8.265625" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -5160,7 +5049,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="B3:O32"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="15.59765625" defaultRowHeight="30" customHeight="1"/>
   <sheetData>
     <row r="3" spans="2:15" ht="30" customHeight="1" thickBot="1">
       <c r="B3" s="26" t="s">
@@ -5342,7 +5231,7 @@
       <c r="N10" s="26"/>
       <c r="O10" s="26"/>
     </row>
-    <row r="11" spans="2:15" s="47" customFormat="1" ht="14.25"/>
+    <row r="11" spans="2:15" s="47" customFormat="1" ht="13.9"/>
     <row r="12" spans="2:15" ht="60" customHeight="1">
       <c r="B12" s="50" t="s">
         <v>100</v>
@@ -5671,17 +5560,17 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Q164"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="9" max="9" width="16.625" style="57" customWidth="1"/>
-    <col min="10" max="10" width="17.25" style="54" customWidth="1"/>
-    <col min="11" max="11" width="19.125" style="55" customWidth="1"/>
+    <col min="9" max="9" width="16.59765625" style="57" customWidth="1"/>
+    <col min="10" max="10" width="17.265625" style="54" customWidth="1"/>
+    <col min="11" max="11" width="19.1328125" style="55" customWidth="1"/>
     <col min="12" max="12" width="14" style="55" customWidth="1"/>
-    <col min="13" max="13" width="14.625" style="56" customWidth="1"/>
-    <col min="14" max="14" width="13.625" style="26" customWidth="1"/>
+    <col min="13" max="13" width="14.59765625" style="56" customWidth="1"/>
+    <col min="14" max="14" width="13.59765625" style="26" customWidth="1"/>
     <col min="15" max="15" width="14" style="26" customWidth="1"/>
-    <col min="16" max="16" width="23.375" style="26" customWidth="1"/>
-    <col min="17" max="17" width="17.875" style="26" customWidth="1"/>
+    <col min="16" max="16" width="23.3984375" style="26" customWidth="1"/>
+    <col min="17" max="17" width="17.86328125" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -9047,16 +8936,16 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="12.75" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.73046875" customWidth="1"/>
+    <col min="4" max="4" width="17.46484375" customWidth="1"/>
+    <col min="5" max="5" width="6.265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" customWidth="1"/>
-    <col min="9" max="10" width="18.25" customWidth="1"/>
-    <col min="14" max="14" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.59765625" customWidth="1"/>
+    <col min="9" max="10" width="18.265625" customWidth="1"/>
+    <col min="14" max="14" width="19.1328125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16" style="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10142,36 +10031,12 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="P2">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="percent" val="100"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="P2:P10">
     <cfRule type="colorScale" priority="5">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P14">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="percent" val="100"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -10181,9 +10046,9 @@
   <conditionalFormatting sqref="P14:P19">
     <cfRule type="colorScale" priority="14">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -10200,11 +10065,11 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.46484375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -11422,9 +11287,9 @@
   <conditionalFormatting sqref="P2:P11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -11434,9 +11299,9 @@
   <conditionalFormatting sqref="P15:P21">
     <cfRule type="colorScale" priority="8">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -11453,12 +11318,12 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="8.25" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.5" customWidth="1"/>
+    <col min="2" max="2" width="8.265625" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.46484375" customWidth="1"/>
     <col min="6" max="12" width="10" customWidth="1"/>
     <col min="13" max="17" width="9" style="8"/>
   </cols>
@@ -12301,23 +12166,441 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBDC588-919F-4704-AFDC-F4184815FDFA}">
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>124</v>
+      </c>
+      <c r="D3">
+        <f>B3+C3</f>
+        <v>144</v>
+      </c>
+      <c r="F3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3">
+        <f>$D3*B$5/$D$5</f>
+        <v>39</v>
+      </c>
+      <c r="H3">
+        <f>$D3*C$5/$D$5</f>
+        <v>105</v>
+      </c>
+      <c r="I3">
+        <f>G3+H3</f>
+        <v>144</v>
+      </c>
+      <c r="K3">
+        <f>(B3-G3)^2/G3</f>
+        <v>9.2564102564102573</v>
+      </c>
+      <c r="L3">
+        <f>(C3-H3)^2/H3</f>
+        <v>3.4380952380952383</v>
+      </c>
+      <c r="N3">
+        <f>SUM(K3:L4)</f>
+        <v>25.389010989010991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4">
+        <v>58</v>
+      </c>
+      <c r="C4">
+        <v>86</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D5" si="0">B4+C4</f>
+        <v>144</v>
+      </c>
+      <c r="F4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4">
+        <f>$D4*B$5/$D$5</f>
+        <v>39</v>
+      </c>
+      <c r="H4">
+        <f>$D4*C$5/$D$5</f>
+        <v>105</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I5" si="1">G4+H4</f>
+        <v>144</v>
+      </c>
+      <c r="K4">
+        <f>(B4-G4)^2/G4</f>
+        <v>9.2564102564102573</v>
+      </c>
+      <c r="L4">
+        <f>(C4-H4)^2/H4</f>
+        <v>3.4380952380952383</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5">
+        <f>B3+B4</f>
+        <v>78</v>
+      </c>
+      <c r="C5">
+        <f>C3+C4</f>
+        <v>210</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>288</v>
+      </c>
+      <c r="F5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5">
+        <f>G3+G4</f>
+        <v>78</v>
+      </c>
+      <c r="H5">
+        <f>H3+H4</f>
+        <v>210</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8">
+        <v>58</v>
+      </c>
+      <c r="C8">
+        <v>86</v>
+      </c>
+      <c r="D8">
+        <f>B8+C8</f>
+        <v>144</v>
+      </c>
+      <c r="F8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8">
+        <f>$D8*B$10/$D$10</f>
+        <v>84.5</v>
+      </c>
+      <c r="H8">
+        <f>$D8*C$10/$D$10</f>
+        <v>59.5</v>
+      </c>
+      <c r="I8">
+        <f>G8+H8</f>
+        <v>144</v>
+      </c>
+      <c r="K8">
+        <f>(B8-G8)^2/G8</f>
+        <v>8.3106508875739653</v>
+      </c>
+      <c r="L8">
+        <f>(C8-H8)^2/H8</f>
+        <v>11.802521008403362</v>
+      </c>
+      <c r="N8">
+        <f>SUM(K8:L9)</f>
+        <v>40.226343791954655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9">
+        <v>111</v>
+      </c>
+      <c r="C9">
+        <v>33</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ref="D9:D10" si="2">B9+C9</f>
+        <v>144</v>
+      </c>
+      <c r="F9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9">
+        <f>$D9*B$10/$D$10</f>
+        <v>84.5</v>
+      </c>
+      <c r="H9">
+        <f>$D9*C$10/$D$10</f>
+        <v>59.5</v>
+      </c>
+      <c r="I9">
+        <f t="shared" ref="I9:I10" si="3">G9+H9</f>
+        <v>144</v>
+      </c>
+      <c r="K9">
+        <f>(B9-G9)^2/G9</f>
+        <v>8.3106508875739653</v>
+      </c>
+      <c r="L9">
+        <f>(C9-H9)^2/H9</f>
+        <v>11.802521008403362</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10">
+        <f>B8+B9</f>
+        <v>169</v>
+      </c>
+      <c r="C10">
+        <f>C8+C9</f>
+        <v>119</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="2"/>
+        <v>288</v>
+      </c>
+      <c r="F10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10">
+        <f>G8+G9</f>
+        <v>169</v>
+      </c>
+      <c r="H10">
+        <f>H8+H9</f>
+        <v>119</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>124</v>
+      </c>
+      <c r="D13">
+        <f>B13+C13</f>
+        <v>144</v>
+      </c>
+      <c r="F13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13">
+        <f>$D13*B$15/$D$15</f>
+        <v>65.5</v>
+      </c>
+      <c r="H13">
+        <f>$D13*C$15/$D$15</f>
+        <v>78.5</v>
+      </c>
+      <c r="I13">
+        <f>G13+H13</f>
+        <v>144</v>
+      </c>
+      <c r="K13">
+        <f>(B13-G13)^2/G13</f>
+        <v>31.606870229007633</v>
+      </c>
+      <c r="L13">
+        <f>(C13-H13)^2/H13</f>
+        <v>26.372611464968152</v>
+      </c>
+      <c r="N13">
+        <f>SUM(K13:L14)</f>
+        <v>115.95896338795157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14">
+        <v>111</v>
+      </c>
+      <c r="C14">
+        <v>33</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ref="D14:D15" si="4">B14+C14</f>
+        <v>144</v>
+      </c>
+      <c r="F14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14">
+        <f>$D14*B$15/$D$15</f>
+        <v>65.5</v>
+      </c>
+      <c r="H14">
+        <f>$D14*C$15/$D$15</f>
+        <v>78.5</v>
+      </c>
+      <c r="I14">
+        <f t="shared" ref="I14:I15" si="5">G14+H14</f>
+        <v>144</v>
+      </c>
+      <c r="K14">
+        <f>(B14-G14)^2/G14</f>
+        <v>31.606870229007633</v>
+      </c>
+      <c r="L14">
+        <f>(C14-H14)^2/H14</f>
+        <v>26.372611464968152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15">
+        <f>B13+B14</f>
+        <v>131</v>
+      </c>
+      <c r="C15">
+        <f>C13+C14</f>
+        <v>157</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="4"/>
+        <v>288</v>
+      </c>
+      <c r="F15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15">
+        <f>G13+G14</f>
+        <v>131</v>
+      </c>
+      <c r="H15">
+        <f>H13+H14</f>
+        <v>157</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="5"/>
+        <v>288</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177AC0FD-BA33-4451-A131-A299D4885FAD}">
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:R164"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="9" max="10" width="16.625" style="57" customWidth="1"/>
-    <col min="11" max="11" width="17.25" style="54" customWidth="1"/>
-    <col min="12" max="12" width="19.125" style="55" customWidth="1"/>
+    <col min="9" max="10" width="16.59765625" style="57" customWidth="1"/>
+    <col min="11" max="11" width="17.265625" style="54" customWidth="1"/>
+    <col min="12" max="12" width="19.1328125" style="55" customWidth="1"/>
     <col min="13" max="13" width="14" style="55" customWidth="1"/>
-    <col min="14" max="14" width="14.625" style="56" customWidth="1"/>
-    <col min="15" max="15" width="13.625" style="26" customWidth="1"/>
-    <col min="16" max="16" width="19.625" style="26" customWidth="1"/>
-    <col min="17" max="17" width="23.375" style="26" customWidth="1"/>
-    <col min="18" max="18" width="17.875" style="26" customWidth="1"/>
+    <col min="14" max="14" width="14.59765625" style="56" customWidth="1"/>
+    <col min="15" max="15" width="13.59765625" style="26" customWidth="1"/>
+    <col min="16" max="16" width="19.59765625" style="26" customWidth="1"/>
+    <col min="17" max="17" width="23.3984375" style="26" customWidth="1"/>
+    <col min="18" max="18" width="17.86328125" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -12783,7 +13066,7 @@
       <c r="G21">
         <v>1</v>
       </c>
-      <c r="N21" s="56">
+      <c r="O21" s="26">
         <v>1</v>
       </c>
     </row>
@@ -13140,7 +13423,7 @@
       <c r="G38">
         <v>1</v>
       </c>
-      <c r="N38" s="56">
+      <c r="P38" s="26">
         <v>1</v>
       </c>
     </row>
@@ -14274,6 +14557,9 @@
       <c r="H92">
         <v>1</v>
       </c>
+      <c r="I92" s="57">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="1:16">
       <c r="A93">
@@ -15031,7 +15317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:15">
       <c r="A129">
         <v>7</v>
       </c>
@@ -15052,7 +15338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:15">
       <c r="A130">
         <v>7</v>
       </c>
@@ -15073,7 +15359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:15">
       <c r="A131">
         <v>7</v>
       </c>
@@ -15094,7 +15380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:15">
       <c r="A132">
         <v>7</v>
       </c>
@@ -15115,7 +15401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:15">
       <c r="A133">
         <v>7</v>
       </c>
@@ -15136,7 +15422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:15">
       <c r="A134">
         <v>7</v>
       </c>
@@ -15157,7 +15443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:15">
       <c r="A135">
         <v>7</v>
       </c>
@@ -15178,7 +15464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:15">
       <c r="A136">
         <v>7</v>
       </c>
@@ -15199,7 +15485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:15">
       <c r="A137">
         <v>7</v>
       </c>
@@ -15220,7 +15506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:15">
       <c r="A138">
         <v>7</v>
       </c>
@@ -15241,7 +15527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:15">
       <c r="A139">
         <v>7</v>
       </c>
@@ -15262,7 +15548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:15">
       <c r="A140">
         <v>7</v>
       </c>
@@ -15283,7 +15569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:15">
       <c r="A141">
         <v>7</v>
       </c>
@@ -15300,11 +15586,11 @@
       <c r="G141">
         <v>1</v>
       </c>
-      <c r="N141" s="56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:14">
+      <c r="O141" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
       <c r="A142">
         <v>7</v>
       </c>
@@ -15325,7 +15611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:15">
       <c r="A143">
         <v>7</v>
       </c>
@@ -15346,7 +15632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:15">
       <c r="A144">
         <v>7</v>
       </c>
@@ -15384,7 +15670,7 @@
       <c r="G145">
         <v>1</v>
       </c>
-      <c r="N145" s="56">
+      <c r="O145" s="26">
         <v>1</v>
       </c>
     </row>
@@ -15426,7 +15712,7 @@
       <c r="F147">
         <v>1</v>
       </c>
-      <c r="L147" s="55">
+      <c r="N147" s="56">
         <v>1</v>
       </c>
     </row>
@@ -15468,7 +15754,7 @@
       <c r="F149">
         <v>1</v>
       </c>
-      <c r="L149" s="55">
+      <c r="N149" s="56">
         <v>1</v>
       </c>
     </row>
@@ -15489,7 +15775,7 @@
       <c r="F150">
         <v>1</v>
       </c>
-      <c r="L150" s="55">
+      <c r="N150" s="56">
         <v>1</v>
       </c>
     </row>
@@ -15797,7 +16083,7 @@
       </c>
       <c r="I164" s="57">
         <f t="shared" ref="I164:N164" si="4">SUM(I2:I163)</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J164" s="57">
         <f t="shared" si="4"/>
@@ -15809,7 +16095,7 @@
       </c>
       <c r="L164" s="55">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M164" s="55">
         <f t="shared" si="4"/>
@@ -15817,15 +16103,15 @@
       </c>
       <c r="N164" s="56">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O164" s="26">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P164" s="26">
         <f>SUM(P2:P163)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q164" s="26">
         <f>SUM(Q2:Q163)</f>
@@ -15849,15 +16135,15 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Q19"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="12.75" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="7" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="18.25" customWidth="1"/>
-    <col min="15" max="15" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.73046875" customWidth="1"/>
+    <col min="4" max="4" width="17.46484375" customWidth="1"/>
+    <col min="5" max="5" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.265625" customWidth="1"/>
+    <col min="7" max="7" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="18.265625" customWidth="1"/>
+    <col min="15" max="15" width="19.1328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16" style="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15936,7 +16222,7 @@
       </c>
       <c r="F2">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A2,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!F$1,result_20260622!$1:$1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A2,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!G$1,result_20260622!$1:$1,0)))</f>
@@ -15960,7 +16246,7 @@
       </c>
       <c r="L2">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A2,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A2,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -16021,7 +16307,7 @@
       </c>
       <c r="J3">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A3,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!J$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A3,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!K$1,result_20260622!$1:$1,0)))</f>
@@ -16029,7 +16315,7 @@
       </c>
       <c r="L3">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A3,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A3,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -16220,7 +16506,7 @@
       </c>
       <c r="H6">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A6,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!H$1,result_20260622!$1:$1,0)))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A6,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!I$1,result_20260622!$1:$1,0)))</f>
@@ -16350,7 +16636,7 @@
       </c>
       <c r="F8">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A8,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!F$1,result_20260622!$1:$1,0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A8,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!G$1,result_20260622!$1:$1,0)))</f>
@@ -16374,7 +16660,7 @@
       </c>
       <c r="L8">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A8,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A8,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -16443,11 +16729,11 @@
       </c>
       <c r="L9">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A9,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A9,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!M$1,result_20260622!$1:$1,0)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A9,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!N$1,result_20260622!$1:$1,0)))</f>
@@ -16488,7 +16774,7 @@
       </c>
       <c r="F10" s="24">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G10" s="24">
         <f t="shared" si="2"/>
@@ -16496,7 +16782,7 @@
       </c>
       <c r="H10" s="24">
         <f t="shared" si="2"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I10" s="24">
         <f t="shared" si="2"/>
@@ -16504,7 +16790,7 @@
       </c>
       <c r="J10" s="24">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" s="24">
         <f t="shared" si="2"/>
@@ -16512,11 +16798,11 @@
       </c>
       <c r="L10" s="24">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M10" s="24">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N10" s="24">
         <f t="shared" si="2"/>
@@ -16615,7 +16901,7 @@
       </c>
       <c r="F14">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A14,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!F$1,result_20260622!$1:$1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A14,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!G$1,result_20260622!$1:$1,0)))</f>
@@ -16639,7 +16925,7 @@
       </c>
       <c r="L14">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A14,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M14">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A14,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -16700,7 +16986,7 @@
       </c>
       <c r="J15">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A15,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!J$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A15,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!K$1,result_20260622!$1:$1,0)))</f>
@@ -16708,7 +16994,7 @@
       </c>
       <c r="L15">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A15,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A15,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -16915,11 +17201,11 @@
       </c>
       <c r="L18">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A18,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A18,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!M$1,result_20260622!$1:$1,0)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18">
         <f>SUMIF(result_20260622!$A:$A,sum_orient_20260622!$A18,INDEX(result_20260622!$A:$Z,0,MATCH(sum_orient_20260622!N$1,result_20260622!$1:$1,0)))</f>
@@ -16960,7 +17246,7 @@
       </c>
       <c r="F19" s="24">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="24">
         <f t="shared" si="4"/>
@@ -16976,7 +17262,7 @@
       </c>
       <c r="J19" s="24">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K19" s="24">
         <f t="shared" si="4"/>
@@ -16984,11 +17270,11 @@
       </c>
       <c r="L19" s="24">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M19" s="24">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" s="24">
         <f t="shared" si="4"/>
@@ -17009,36 +17295,12 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="Q2">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="percent" val="100"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q10">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q14">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="percent" val="100"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -17048,9 +17310,9 @@
   <conditionalFormatting sqref="Q14:Q19">
     <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -17067,11 +17329,11 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Q21"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.46484375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -17161,7 +17423,7 @@
       </c>
       <c r="I2">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A2,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!I$1,result_20260622!$1:$1,0)))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A2,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!J$1,result_20260622!$1:$1,0)))</f>
@@ -17173,11 +17435,11 @@
       </c>
       <c r="L2">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A2,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A2,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A2,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!N$1,result_20260622!$1:$1,0)))</f>
@@ -17311,11 +17573,11 @@
       </c>
       <c r="L4">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A4,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A4,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A4,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!N$1,result_20260622!$1:$1,0)))</f>
@@ -17372,7 +17634,7 @@
       </c>
       <c r="J5">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A5,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!J$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A5,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!K$1,result_20260622!$1:$1,0)))</f>
@@ -17380,7 +17642,7 @@
       </c>
       <c r="L5">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A5,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A5,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -17563,7 +17825,7 @@
       </c>
       <c r="F8">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A8,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!F$1,result_20260622!$1:$1,0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A8,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!G$1,result_20260622!$1:$1,0)))</f>
@@ -17587,7 +17849,7 @@
       </c>
       <c r="L8">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A8,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M8">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A8,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -17701,7 +17963,7 @@
       </c>
       <c r="F10">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A10,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!F$1,result_20260622!$1:$1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A10,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!G$1,result_20260622!$1:$1,0)))</f>
@@ -17725,7 +17987,7 @@
       </c>
       <c r="L10">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A10,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A10,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -17770,7 +18032,7 @@
       </c>
       <c r="F11" s="24">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G11" s="24">
         <f t="shared" si="2"/>
@@ -17782,11 +18044,11 @@
       </c>
       <c r="I11" s="24">
         <f t="shared" si="2"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J11" s="24">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="24">
         <f t="shared" si="2"/>
@@ -17794,11 +18056,11 @@
       </c>
       <c r="L11" s="24">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M11" s="24">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N11" s="24">
         <f t="shared" si="2"/>
@@ -17909,7 +18171,7 @@
       </c>
       <c r="I15">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A15,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!I$1,result_20260622!$1:$1,0)))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A15,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!J$1,result_20260622!$1:$1,0)))</f>
@@ -17921,11 +18183,11 @@
       </c>
       <c r="L15">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A15,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A15,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N15">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A15,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!N$1,result_20260622!$1:$1,0)))</f>
@@ -17990,11 +18252,11 @@
       </c>
       <c r="L16">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A16,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A16,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N16">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A16,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!N$1,result_20260622!$1:$1,0)))</f>
@@ -18051,7 +18313,7 @@
       </c>
       <c r="J17">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A17,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!J$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A17,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!K$1,result_20260622!$1:$1,0)))</f>
@@ -18059,7 +18321,7 @@
       </c>
       <c r="L17">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A17,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A17,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -18173,7 +18435,7 @@
       </c>
       <c r="F19">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A19,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!F$1,result_20260622!$1:$1,0)))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A19,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!G$1,result_20260622!$1:$1,0)))</f>
@@ -18197,7 +18459,7 @@
       </c>
       <c r="L19">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A19,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M19">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A19,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -18242,7 +18504,7 @@
       </c>
       <c r="F20">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A20,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!F$1,result_20260622!$1:$1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A20,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!G$1,result_20260622!$1:$1,0)))</f>
@@ -18266,7 +18528,7 @@
       </c>
       <c r="L20">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A20,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!L$1,result_20260622!$1:$1,0)))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20">
         <f>SUMIF(result_20260622!$B:$B,sum_pos_20260622!$A20,INDEX(result_20260622!$A:$Z,0,MATCH(sum_pos_20260622!M$1,result_20260622!$1:$1,0)))</f>
@@ -18311,7 +18573,7 @@
       </c>
       <c r="F21" s="24">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G21" s="24">
         <f t="shared" si="6"/>
@@ -18323,11 +18585,11 @@
       </c>
       <c r="I21" s="24">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J21" s="24">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K21" s="24">
         <f t="shared" si="6"/>
@@ -18335,11 +18597,11 @@
       </c>
       <c r="L21" s="24">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M21" s="24">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N21" s="24">
         <f t="shared" si="6"/>
@@ -18363,9 +18625,9 @@
   <conditionalFormatting sqref="Q2:Q11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -18375,9 +18637,9 @@
   <conditionalFormatting sqref="Q15:Q21">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -18394,12 +18656,12 @@
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:S27"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="8.25" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.5" customWidth="1"/>
+    <col min="2" max="2" width="8.265625" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.46484375" customWidth="1"/>
     <col min="6" max="12" width="10" customWidth="1"/>
     <col min="13" max="17" width="9" style="8"/>
   </cols>
@@ -18460,11 +18722,11 @@
       </c>
       <c r="B2">
         <f>result_20260622!I164</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C2" s="8">
         <f t="shared" ref="C2:C11" si="0">B2/$B$21</f>
-        <v>0.69753086419753085</v>
+        <v>0.70370370370370372</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -18487,11 +18749,11 @@
       </c>
       <c r="K2" cm="1">
         <f t="array" ref="K2">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F2)*result_20260622!$N$2:$N$200)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" s="77" cm="1">
         <f t="array" ref="L2">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F2)*result_20260622!$O$2:$R$200)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2" s="81">
         <f>H2/$G2</f>
@@ -18507,11 +18769,11 @@
       </c>
       <c r="P2" s="67">
         <f t="shared" si="1"/>
-        <v>0.125</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="Q2" s="86">
         <f t="shared" si="1"/>
-        <v>0.20833333333333334</v>
+        <v>0.25</v>
       </c>
       <c r="R2" t="s">
         <v>82</v>
@@ -18550,11 +18812,11 @@
       </c>
       <c r="K3" cm="1">
         <f t="array" ref="K3">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F3)*result_20260622!$N$2:$N$200)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" s="77" cm="1">
         <f t="array" ref="L3">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F3)*result_20260622!$O$2:$R$200)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" s="81">
         <f t="shared" ref="M3:M9" si="2">H3/$G3</f>
@@ -18570,11 +18832,11 @@
       </c>
       <c r="P3" s="67">
         <f t="shared" si="1"/>
-        <v>0.1111111111111111</v>
+        <v>7.407407407407407E-2</v>
       </c>
       <c r="Q3" s="86">
         <f t="shared" si="1"/>
-        <v>0.1111111111111111</v>
+        <v>0.14814814814814814</v>
       </c>
       <c r="R3" t="s">
         <v>82</v>
@@ -18649,11 +18911,11 @@
       </c>
       <c r="B5">
         <f>result_20260622!L164</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" s="8">
         <f t="shared" si="0"/>
-        <v>8.6419753086419748E-2</v>
+        <v>6.7901234567901231E-2</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -18723,11 +18985,11 @@
       </c>
       <c r="G6" cm="1">
         <f t="array" ref="G6">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F6)*result_20260622!$I$2:$R$200)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" s="76" cm="1">
         <f t="array" ref="H6">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F6)*result_20260622!$I$2:$J$200)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" cm="1">
         <f t="array" ref="I6">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F6)*result_20260622!$K$2:$K$200)</f>
@@ -18747,7 +19009,7 @@
       </c>
       <c r="M6" s="81">
         <f t="shared" si="2"/>
-        <v>0.82352941176470584</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="N6" s="65">
         <f t="shared" si="1"/>
@@ -18759,11 +19021,11 @@
       </c>
       <c r="P6" s="67">
         <f t="shared" si="1"/>
-        <v>0.11764705882352941</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="Q6" s="86">
         <f t="shared" si="1"/>
-        <v>5.8823529411764705E-2</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="R6" t="s">
         <v>82</v>
@@ -18775,11 +19037,11 @@
       </c>
       <c r="B7">
         <f>result_20260622!N164</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="8">
         <f t="shared" si="0"/>
-        <v>6.7901234567901231E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -18838,11 +19100,11 @@
       </c>
       <c r="B8">
         <f>result_20260622!O164</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="8">
         <f t="shared" si="0"/>
-        <v>6.1728395061728392E-3</v>
+        <v>2.4691358024691357E-2</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -18865,11 +19127,11 @@
       </c>
       <c r="K8" cm="1">
         <f t="array" ref="K8">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F8)*result_20260622!$N$2:$N$200)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="77" cm="1">
         <f t="array" ref="L8">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F8)*result_20260622!$O$2:$R$200)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="64">
         <f t="shared" si="2"/>
@@ -18885,11 +19147,11 @@
       </c>
       <c r="P8" s="67">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="68">
+        <f t="shared" si="1"/>
         <v>0.1111111111111111</v>
-      </c>
-      <c r="Q8" s="68">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="R8" t="s">
         <v>84</v>
@@ -18901,11 +19163,11 @@
       </c>
       <c r="B9">
         <f>result_20260622!P164</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="8">
         <f t="shared" si="0"/>
-        <v>4.9382716049382713E-2</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -18924,11 +19186,11 @@
       </c>
       <c r="J9" cm="1">
         <f t="array" ref="J9">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F9)*result_20260622!$L$2:$M$200)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" cm="1">
         <f t="array" ref="K9">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F9)*result_20260622!$N$2:$N$200)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" s="77" cm="1">
         <f t="array" ref="L9">SUMPRODUCT((result_20260622!$A$2:$A$200=sum_fail_20260622!$F9)*result_20260622!$O$2:$R$200)</f>
@@ -18944,11 +19206,11 @@
       </c>
       <c r="O9" s="71">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="72">
+        <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
-      </c>
-      <c r="P9" s="72">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="Q9" s="87">
         <f t="shared" si="1"/>
@@ -18972,11 +19234,11 @@
       </c>
       <c r="G10">
         <f t="shared" ref="G10:L10" si="3">SUM(G2:G9)</f>
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H10">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I10">
         <f t="shared" si="3"/>
@@ -18984,15 +19246,15 @@
       </c>
       <c r="J10">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K10">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -19103,15 +19365,15 @@
       </c>
       <c r="B23">
         <f>result_20260622!I164+result_20260622!J164</f>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" s="8">
         <f>B23/$B$21</f>
-        <v>0.70987654320987659</v>
+        <v>0.71604938271604934</v>
       </c>
       <c r="D23" s="8">
         <f>B23/$B$20</f>
-        <v>0.8214285714285714</v>
+        <v>0.82857142857142863</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -19137,15 +19399,15 @@
       </c>
       <c r="B25">
         <f>result_20260622!L164+result_20260622!M164</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C25" s="8">
         <f>B25/$B$21</f>
-        <v>8.6419753086419748E-2</v>
+        <v>6.7901234567901231E-2</v>
       </c>
       <c r="D25" s="8">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>7.857142857142857E-2</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -19154,15 +19416,15 @@
       </c>
       <c r="B26">
         <f>result_20260622!N164</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="8">
         <f>B26/$B$21</f>
-        <v>6.7901234567901231E-2</v>
+        <v>6.1728395061728392E-2</v>
       </c>
       <c r="D26" s="8">
         <f t="shared" si="4"/>
-        <v>7.857142857142857E-2</v>
+        <v>7.1428571428571425E-2</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -19171,11 +19433,11 @@
       </c>
       <c r="B27">
         <f>result_20260622!O164+result_20260622!P164+result_20260622!Q164+result_20260622!R164</f>
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C27" s="8">
         <f>B27/$B$21</f>
-        <v>0.1111111111111111</v>
+        <v>0.13580246913580246</v>
       </c>
       <c r="D27" s="8"/>
     </row>
@@ -19278,7 +19540,7 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="B3:O32"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="15.59765625" defaultRowHeight="30" customHeight="1"/>
   <sheetData>
     <row r="3" spans="2:15" ht="30" customHeight="1" thickBot="1">
       <c r="B3" s="26" t="s">
@@ -19460,7 +19722,7 @@
       <c r="N10" s="26"/>
       <c r="O10" s="26"/>
     </row>
-    <row r="11" spans="2:15" s="47" customFormat="1" ht="14.25"/>
+    <row r="11" spans="2:15" s="47" customFormat="1" ht="13.9"/>
     <row r="12" spans="2:15" ht="60" customHeight="1">
       <c r="B12" s="50" t="s">
         <v>64</v>
@@ -19609,35 +19871,35 @@
     </row>
     <row r="19" spans="3:14" ht="30" customHeight="1" thickBot="1">
       <c r="G19" s="22">
-        <f>[1]sum_orient_20260605!P2</f>
+        <f>sum_orient_20260605!P2</f>
         <v>0.59259259259259256</v>
       </c>
       <c r="H19" s="9">
-        <f>[1]sum_orient_20260605!P3</f>
+        <f>sum_orient_20260605!P3</f>
         <v>7.407407407407407E-2</v>
       </c>
       <c r="I19" s="9">
-        <f>[1]sum_orient_20260605!P4</f>
+        <f>sum_orient_20260605!P4</f>
         <v>0</v>
       </c>
       <c r="J19" s="9">
-        <f>[1]sum_orient_20260605!P5</f>
+        <f>sum_orient_20260605!P5</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="K19" s="9">
-        <f>[1]sum_orient_20260605!P6</f>
+        <f>sum_orient_20260605!P6</f>
         <v>0.3888888888888889</v>
       </c>
       <c r="L19" s="9">
-        <f>[1]sum_orient_20260605!P7</f>
+        <f>sum_orient_20260605!P7</f>
         <v>0.3888888888888889</v>
       </c>
       <c r="M19" s="9">
-        <f>[1]sum_orient_20260605!P8</f>
+        <f>sum_orient_20260605!P8</f>
         <v>0.22222222222222221</v>
       </c>
       <c r="N19" s="23">
-        <f>[1]sum_orient_20260605!P9</f>
+        <f>sum_orient_20260605!P9</f>
         <v>0.72222222222222221</v>
       </c>
     </row>
@@ -19678,15 +19940,15 @@
     </row>
     <row r="21" spans="3:14" ht="30" customHeight="1">
       <c r="C21" s="15">
-        <f>[1]sum_pos_20260605!P2</f>
+        <f>sum_pos_20260605!P2</f>
         <v>0.45833333333333331</v>
       </c>
       <c r="D21" s="11">
-        <f>[1]sum_pos_20260605!P5</f>
+        <f>sum_pos_20260605!P5</f>
         <v>0.375</v>
       </c>
       <c r="E21" s="16">
-        <f>[1]sum_pos_20260605!P8</f>
+        <f>sum_pos_20260605!P8</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
@@ -19703,15 +19965,15 @@
     </row>
     <row r="23" spans="3:14" ht="15" customHeight="1">
       <c r="C23" s="15">
-        <f>[1]sum_pos_20260605!P3</f>
+        <f>sum_pos_20260605!P3</f>
         <v>0.5</v>
       </c>
       <c r="D23" s="11">
-        <f>[1]sum_pos_20260605!P6</f>
+        <f>sum_pos_20260605!P6</f>
         <v>0.5</v>
       </c>
       <c r="E23" s="16">
-        <f>[1]sum_pos_20260605!P9</f>
+        <f>sum_pos_20260605!P9</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -19728,15 +19990,15 @@
     </row>
     <row r="25" spans="3:14" ht="30" customHeight="1" thickBot="1">
       <c r="C25" s="19">
-        <f>[1]sum_pos_20260605!P4</f>
+        <f>sum_pos_20260605!P4</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="D25" s="20">
-        <f>[1]sum_pos_20260605!P7</f>
+        <f>sum_pos_20260605!P7</f>
         <v>0.5</v>
       </c>
       <c r="E25" s="21">
-        <f>[1]sum_pos_20260605!P10</f>
+        <f>sum_pos_20260605!P10</f>
         <v>0.41666666666666669</v>
       </c>
     </row>
@@ -19785,21 +20047,21 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB563E77-EE44-42B3-ACD0-800B48D3E7DF}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:Q164"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="9" max="9" width="17.25" style="57" customWidth="1"/>
-    <col min="10" max="10" width="15.375" style="57" customWidth="1"/>
-    <col min="11" max="11" width="17.5" style="57" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="54" customWidth="1"/>
+    <col min="9" max="9" width="17.265625" style="57" customWidth="1"/>
+    <col min="10" max="10" width="15.3984375" style="57" customWidth="1"/>
+    <col min="11" max="11" width="17.46484375" style="57" customWidth="1"/>
+    <col min="12" max="12" width="17.265625" style="54" customWidth="1"/>
     <col min="13" max="13" width="14" style="54" customWidth="1"/>
-    <col min="14" max="14" width="19.125" style="58" customWidth="1"/>
-    <col min="15" max="15" width="14.625" style="56" customWidth="1"/>
-    <col min="16" max="16" width="13.625" style="26" customWidth="1"/>
-    <col min="17" max="17" width="18.125" style="26" customWidth="1"/>
+    <col min="14" max="14" width="19.1328125" style="58" customWidth="1"/>
+    <col min="15" max="15" width="14.59765625" style="56" customWidth="1"/>
+    <col min="16" max="16" width="13.59765625" style="26" customWidth="1"/>
+    <col min="17" max="17" width="18.1328125" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -19876,7 +20138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1">
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>1</v>
       </c>
@@ -19894,7 +20156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1">
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>1</v>
       </c>
@@ -19912,7 +20174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1">
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>1</v>
       </c>
@@ -19930,7 +20192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>1</v>
       </c>
@@ -19948,7 +20210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>1</v>
       </c>
@@ -20029,7 +20291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1">
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>1</v>
       </c>
@@ -20047,7 +20309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1">
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>1</v>
       </c>
@@ -20065,7 +20327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1">
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>1</v>
       </c>
@@ -20083,7 +20345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1">
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>1</v>
       </c>
@@ -20101,7 +20363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1">
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>1</v>
       </c>
@@ -20119,7 +20381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1">
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>1</v>
       </c>
@@ -20158,7 +20420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1">
+    <row r="18" spans="1:17">
       <c r="A18">
         <v>1</v>
       </c>
@@ -20197,7 +20459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1">
+    <row r="20" spans="1:17">
       <c r="A20">
         <v>1</v>
       </c>
@@ -20260,7 +20522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1">
+    <row r="23" spans="1:17">
       <c r="A23">
         <v>1</v>
       </c>
@@ -20320,7 +20582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1">
+    <row r="26" spans="1:17">
       <c r="A26">
         <v>1</v>
       </c>
@@ -20338,7 +20600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1">
+    <row r="27" spans="1:17">
       <c r="A27">
         <v>1</v>
       </c>
@@ -20419,7 +20681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1">
+    <row r="31" spans="1:17">
       <c r="A31">
         <v>2</v>
       </c>
@@ -20692,7 +20954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>2</v>
       </c>
@@ -21322,7 +21584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1">
+    <row r="74" spans="1:16">
       <c r="A74">
         <v>4</v>
       </c>
@@ -21343,7 +21605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1">
+    <row r="75" spans="1:16">
       <c r="A75">
         <v>4</v>
       </c>
@@ -21364,7 +21626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1">
+    <row r="76" spans="1:16">
       <c r="A76">
         <v>4</v>
       </c>
@@ -21385,7 +21647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1">
+    <row r="77" spans="1:16">
       <c r="A77">
         <v>4</v>
       </c>
@@ -21406,7 +21668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1">
+    <row r="78" spans="1:16">
       <c r="A78">
         <v>4</v>
       </c>
@@ -21427,7 +21689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1">
+    <row r="79" spans="1:16">
       <c r="A79">
         <v>4</v>
       </c>
@@ -21445,7 +21707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1">
+    <row r="80" spans="1:16">
       <c r="A80">
         <v>4</v>
       </c>
@@ -21466,7 +21728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" hidden="1">
+    <row r="81" spans="1:17">
       <c r="A81">
         <v>4</v>
       </c>
@@ -21487,7 +21749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" hidden="1">
+    <row r="82" spans="1:17">
       <c r="A82">
         <v>4</v>
       </c>
@@ -21508,7 +21770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" hidden="1">
+    <row r="83" spans="1:17">
       <c r="A83">
         <v>4</v>
       </c>
@@ -21529,7 +21791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" hidden="1">
+    <row r="84" spans="1:17">
       <c r="A84">
         <v>4</v>
       </c>
@@ -21550,7 +21812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" hidden="1">
+    <row r="85" spans="1:17">
       <c r="A85">
         <v>4</v>
       </c>
@@ -21592,7 +21854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" hidden="1">
+    <row r="87" spans="1:17">
       <c r="A87">
         <v>4</v>
       </c>
@@ -21613,7 +21875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1">
+    <row r="88" spans="1:17">
       <c r="A88">
         <v>4</v>
       </c>
@@ -21634,7 +21896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1">
+    <row r="89" spans="1:17">
       <c r="A89">
         <v>4</v>
       </c>
@@ -21676,7 +21938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" hidden="1">
+    <row r="91" spans="1:17">
       <c r="A91">
         <v>4</v>
       </c>
@@ -21697,7 +21959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" hidden="1">
+    <row r="92" spans="1:17">
       <c r="A92">
         <v>5</v>
       </c>
@@ -21739,7 +22001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" hidden="1">
+    <row r="94" spans="1:17">
       <c r="A94">
         <v>5</v>
       </c>
@@ -21757,7 +22019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" hidden="1">
+    <row r="95" spans="1:17">
       <c r="A95">
         <v>5</v>
       </c>
@@ -21838,7 +22100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1">
+    <row r="99" spans="1:16">
       <c r="A99">
         <v>5</v>
       </c>
@@ -21898,7 +22160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1">
+    <row r="102" spans="1:16">
       <c r="A102">
         <v>5</v>
       </c>
@@ -21916,7 +22178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1">
+    <row r="103" spans="1:16">
       <c r="A103">
         <v>5</v>
       </c>
@@ -21997,7 +22259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1">
+    <row r="107" spans="1:16">
       <c r="A107">
         <v>5</v>
       </c>
@@ -22078,7 +22340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1">
+    <row r="111" spans="1:16">
       <c r="A111">
         <v>6</v>
       </c>
@@ -22099,7 +22361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1">
+    <row r="112" spans="1:16">
       <c r="A112">
         <v>6</v>
       </c>
@@ -22120,7 +22382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1">
+    <row r="113" spans="1:16">
       <c r="A113">
         <v>6</v>
       </c>
@@ -22246,7 +22508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1">
+    <row r="119" spans="1:16">
       <c r="A119">
         <v>6</v>
       </c>
@@ -22288,7 +22550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1">
+    <row r="121" spans="1:16">
       <c r="A121">
         <v>6</v>
       </c>
@@ -22351,7 +22613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1">
+    <row r="124" spans="1:16">
       <c r="A124">
         <v>6</v>
       </c>
@@ -22414,7 +22676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1">
+    <row r="127" spans="1:16">
       <c r="A127">
         <v>6</v>
       </c>
@@ -22498,7 +22760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1">
+    <row r="131" spans="1:16">
       <c r="A131">
         <v>7</v>
       </c>
@@ -22540,7 +22802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1">
+    <row r="133" spans="1:16">
       <c r="A133">
         <v>7</v>
       </c>
@@ -22687,7 +22949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1">
+    <row r="140" spans="1:16">
       <c r="A140">
         <v>7</v>
       </c>
@@ -22750,7 +23012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1">
+    <row r="143" spans="1:16">
       <c r="A143">
         <v>7</v>
       </c>
@@ -22855,7 +23117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" hidden="1">
+    <row r="148" spans="1:17">
       <c r="A148">
         <v>8</v>
       </c>
@@ -22897,7 +23159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1">
+    <row r="150" spans="1:17">
       <c r="A150">
         <v>8</v>
       </c>
@@ -22957,7 +23219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" hidden="1">
+    <row r="153" spans="1:17">
       <c r="A153">
         <v>8</v>
       </c>
@@ -22978,7 +23240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" hidden="1">
+    <row r="154" spans="1:17">
       <c r="A154">
         <v>8</v>
       </c>
@@ -22999,7 +23261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" hidden="1">
+    <row r="155" spans="1:17">
       <c r="A155">
         <v>8</v>
       </c>
@@ -23020,7 +23282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" hidden="1">
+    <row r="156" spans="1:17">
       <c r="A156">
         <v>8</v>
       </c>
@@ -23041,7 +23303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" hidden="1">
+    <row r="157" spans="1:17">
       <c r="A157">
         <v>8</v>
       </c>
@@ -23062,7 +23324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" hidden="1">
+    <row r="158" spans="1:17">
       <c r="A158">
         <v>8</v>
       </c>
@@ -23083,7 +23345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" hidden="1">
+    <row r="159" spans="1:17">
       <c r="A159">
         <v>8</v>
       </c>
@@ -23104,7 +23366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" hidden="1">
+    <row r="160" spans="1:17">
       <c r="A160">
         <v>8</v>
       </c>
@@ -23125,7 +23387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" hidden="1">
+    <row r="161" spans="1:17">
       <c r="A161">
         <v>8</v>
       </c>
@@ -23143,7 +23405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" hidden="1">
+    <row r="162" spans="1:17">
       <c r="A162">
         <v>8</v>
       </c>
@@ -23161,7 +23423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" hidden="1">
+    <row r="163" spans="1:17">
       <c r="A163">
         <v>8</v>
       </c>
@@ -23182,7 +23444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" hidden="1">
+    <row r="164" spans="1:17">
       <c r="A164" t="s">
         <v>37</v>
       </c>
@@ -23249,13 +23511,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q164" xr:uid="{BB563E77-EE44-42B3-ACD0-800B48D3E7DF}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Q164" xr:uid="{BB563E77-EE44-42B3-ACD0-800B48D3E7DF}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -23267,16 +23523,16 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="12.75" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" customWidth="1"/>
-    <col min="9" max="10" width="18.25" customWidth="1"/>
-    <col min="14" max="14" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.73046875" customWidth="1"/>
+    <col min="4" max="4" width="17.46484375" customWidth="1"/>
+    <col min="5" max="5" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.59765625" customWidth="1"/>
+    <col min="9" max="10" width="18.265625" customWidth="1"/>
+    <col min="14" max="14" width="19.1328125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16" style="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -24362,36 +24618,12 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="P2">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="percent" val="100"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="P2:P10">
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P14">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="percent" val="100"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -24401,9 +24633,9 @@
   <conditionalFormatting sqref="P14:P19">
     <cfRule type="colorScale" priority="17">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -24420,11 +24652,11 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="3" max="3" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.46484375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -25642,9 +25874,9 @@
   <conditionalFormatting sqref="P2:P11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -25654,9 +25886,9 @@
   <conditionalFormatting sqref="P15:P21">
     <cfRule type="colorScale" priority="11">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
